--- a/artfynd/A 48189-2025 artfynd.xlsx
+++ b/artfynd/A 48189-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89593694</v>
+        <v>89593711</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436302.0067913078</v>
+        <v>436304</v>
       </c>
       <c r="R2" t="n">
-        <v>7004689.147347278</v>
+        <v>7004691</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2020-09-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-09-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89593711</v>
+        <v>89593704</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436303.8518773605</v>
+        <v>436303</v>
       </c>
       <c r="R3" t="n">
-        <v>7004690.918704925</v>
+        <v>7004692</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2020-09-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-09-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89593691</v>
+        <v>89593694</v>
       </c>
       <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436305.1555957512</v>
+        <v>436302</v>
       </c>
       <c r="R4" t="n">
-        <v>7004688.181461053</v>
+        <v>7004689</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +945,9 @@
           <t>2020-09-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-09-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89593704</v>
+        <v>89593715</v>
       </c>
       <c r="B5" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1204</v>
+        <v>102613</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436302.9649335441</v>
+        <v>436302</v>
       </c>
       <c r="R5" t="n">
-        <v>7004691.840031093</v>
+        <v>7004688</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,19 +1046,9 @@
           <t>2020-09-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-09-17</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,112 +1072,6 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>89593715</v>
-      </c>
-      <c r="B6" t="n">
-        <v>56503</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>102613</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Orre</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Lyrurus tetrix</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Järvdalen utökn öst, Jmt</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>436302</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7004688</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Hallen</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2020-09-03</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2020-09-17</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>

--- a/artfynd/A 48189-2025 artfynd.xlsx
+++ b/artfynd/A 48189-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89593711</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89593704</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89593694</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,8 +1096,19 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89593715</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>